--- a/data/trans_camb/IMC_inf_MED_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R3-Clase-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-2.440181729141675</v>
+        <v>-1.594099310768957</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-12.12783431938141</v>
+        <v>-8.853950736567599</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-7.390973510076243</v>
+        <v>-7.853525717310205</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-11.85344529888112</v>
+        <v>-10.91401280577556</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-4.719871797451983</v>
+        <v>-4.617570537852467</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-12.07164860309319</v>
+        <v>-10.04182324974694</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-14.52843729473054</v>
+        <v>-11.75554989450029</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-23.45341715347141</v>
+        <v>-19.06685568127815</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-18.93358852115257</v>
+        <v>-16.88551660559891</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-22.91726093189643</v>
+        <v>-20.89606006829417</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-13.12101507338952</v>
+        <v>-12.45953816036574</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-20.13314294496347</v>
+        <v>-17.9372559190127</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>9.466845969558326</v>
+        <v>8.421663328557338</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-1.296207953066962</v>
+        <v>0.5550501508467268</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6.973585305332611</v>
+        <v>3.982945521123193</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.2919512916535192</v>
+        <v>2.051277930471796</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>3.020410712057902</v>
+        <v>2.483170408402716</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-4.346929166832873</v>
+        <v>-2.228885758066067</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.1119634446219125</v>
+        <v>-0.08818716750252883</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.5564643362358992</v>
+        <v>-0.4898094060953977</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.3307670457390505</v>
+        <v>-0.3707625923447556</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.5304753261522511</v>
+        <v>-0.5152472693677145</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2136643410644238</v>
+        <v>-0.2343501253198562</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.5464726490523748</v>
+        <v>-0.5096408420243673</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.5042119795558186</v>
+        <v>-0.5127865324889229</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.82511263157366</v>
+        <v>-0.8168811673652489</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.6730811164855995</v>
+        <v>-0.6514486223282204</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.835874516792751</v>
+        <v>-0.8185026091128373</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.4963145975641897</v>
+        <v>-0.509771959797202</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.7702065142225977</v>
+        <v>-0.7433491831698973</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.6563068956141477</v>
+        <v>0.6525001456598937</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.004295432736098586</v>
+        <v>0.09708126086314774</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.4545706554838837</v>
+        <v>0.2684816664652289</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1338749027631417</v>
+        <v>0.2546133655563464</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1781953401915397</v>
+        <v>0.1572284040426176</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.1859082789087763</v>
+        <v>-0.1052701422507669</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-11.31725916734128</v>
+        <v>-8.83869703493159</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-9.339752108910728</v>
+        <v>-6.791480610450576</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-12.10119574014152</v>
+        <v>-8.971217047240344</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-10.28302398411468</v>
+        <v>-9.115980332560415</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-11.32743054305758</v>
+        <v>-8.747382326592405</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-9.679303292949164</v>
+        <v>-8.028488857406987</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-21.94345439736812</v>
+        <v>-18.74748932422673</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-23.40533889541861</v>
+        <v>-18.76239861061883</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-21.44724738008985</v>
+        <v>-17.54247685393242</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-20.5858736788757</v>
+        <v>-19.10768548626784</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-17.82912212563993</v>
+        <v>-15.47801460853912</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-17.03699921710855</v>
+        <v>-15.55720851149047</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-0.9229675368838874</v>
+        <v>0.6921802595449525</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3.526473987086399</v>
+        <v>6.176683142645747</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-2.770579183649027</v>
+        <v>-0.9210128503367085</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1586970033139029</v>
+        <v>-0.05831269627821861</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-4.111336962580166</v>
+        <v>-2.184953689068622</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.5364629234510065</v>
+        <v>0.1704117577940526</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.4317536019276954</v>
+        <v>-0.3775836149179261</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.3563116788710361</v>
+        <v>-0.2901278083640956</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.6389114124461354</v>
+        <v>-0.5212911552252117</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.542916709967321</v>
+        <v>-0.5297029258736445</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.5027657187240779</v>
+        <v>-0.429590582939062</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.429613923327959</v>
+        <v>-0.3942851792230735</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.6793601847158549</v>
+        <v>-0.6464681898537346</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.7194125363986286</v>
+        <v>-0.6834135719831729</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.8462916018075264</v>
+        <v>-0.7743085212051593</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.8246242211267955</v>
+        <v>-0.8392545961106229</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.665357392326267</v>
+        <v>-0.6382464354913145</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.6742965377072769</v>
+        <v>-0.6670748584513799</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.02804501817160446</v>
+        <v>0.06247977791569997</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.1836961981836517</v>
+        <v>0.3646191066595411</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.1836934704434784</v>
+        <v>-0.03469522729781108</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.1065556544076086</v>
+        <v>0.08688445823777619</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1975001879325734</v>
+        <v>-0.1222959200619909</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.01467271035209291</v>
+        <v>0.02682045306522284</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-3.655975015883612</v>
+        <v>-1.798338138529687</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-6.245155981341533</v>
+        <v>-4.606617086239956</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-10.10721742498635</v>
+        <v>-7.513886173853421</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-8.664474707945836</v>
+        <v>-5.804846130702101</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-5.889713744054853</v>
+        <v>-3.751938047940043</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-5.848061836028237</v>
+        <v>-3.986291534582312</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-17.78237367359827</v>
+        <v>-14.53285014700072</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-22.5647832112468</v>
+        <v>-16.87766532176235</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-21.45305476511211</v>
+        <v>-16.95804099069991</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-21.26935197608849</v>
+        <v>-17.0826110443229</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-15.21305958628491</v>
+        <v>-12.0589179567311</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-16.73941883317387</v>
+        <v>-13.49729777959721</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>11.34695125329561</v>
+        <v>10.75590045481883</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>9.253053029400858</v>
+        <v>13.71740789562954</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.2598576786553912</v>
+        <v>3.034469901516446</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>7.723512637205186</v>
+        <v>11.35386809891848</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2.981565265808879</v>
+        <v>4.539974601201513</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>7.689382156654974</v>
+        <v>8.662817089222715</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.1172302551696616</v>
+        <v>-0.06382538057591985</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.2002533458478956</v>
+        <v>-0.1634948858601135</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.4964223904595229</v>
+        <v>-0.4034702671572908</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4255611674051188</v>
+        <v>-0.3117005987276261</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.2288112359360862</v>
+        <v>-0.1613122375487987</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2271930886085889</v>
+        <v>-0.1713881196195015</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.4636777709504098</v>
+        <v>-0.4222136191960446</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.6430105310537644</v>
+        <v>-0.5355369291596005</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.8313671435384538</v>
+        <v>-0.7228278007790476</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.8647942286484335</v>
+        <v>-0.7911707289106716</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.506207264166933</v>
+        <v>-0.4508935104105968</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.5732858875068582</v>
+        <v>-0.5357804160323257</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.4912910325934144</v>
+        <v>0.4995873008209318</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.3672055594221003</v>
+        <v>0.5848659796480967</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.09285201701239393</v>
+        <v>0.2896724212590617</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.6381729235843784</v>
+        <v>0.8223542324465795</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.159487612192999</v>
+        <v>0.2373248821079952</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.3761864264613033</v>
+        <v>0.4472271353347966</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-7.712431297606917</v>
+        <v>-6.412314208829911</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-7.739643127267948</v>
+        <v>-7.002257189890898</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-7.657711101732664</v>
+        <v>-8.208352876693393</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-12.56518418860203</v>
+        <v>-11.52238581635693</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-7.971637802419792</v>
+        <v>-7.461658974373314</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-10.21422079276805</v>
+        <v>-9.201336180399707</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-16.09981499830095</v>
+        <v>-13.61111442864195</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-16.94385617401313</v>
+        <v>-16.84801858133956</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-14.99755876624053</v>
+        <v>-15.21995472964674</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-20.84687560842629</v>
+        <v>-18.85492757086965</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-13.0603998850517</v>
+        <v>-12.27762144231381</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-16.80553391021389</v>
+        <v>-15.6061796686299</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.5348607984218293</v>
+        <v>1.49889243789275</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>3.222666396586916</v>
+        <v>2.659182040548802</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.006050768848189374</v>
+        <v>-1.908014958002727</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-4.990417917283605</v>
+        <v>-3.658554832630667</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-1.801929367764575</v>
+        <v>-2.428045067550594</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-3.628955927947369</v>
+        <v>-2.7542839367055</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.2670206622061218</v>
+        <v>-0.2379229805113096</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.2679627932275266</v>
+        <v>-0.2598122684991747</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.3286523111728033</v>
+        <v>-0.3735838386171476</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.5392703862857463</v>
+        <v>-0.5244142385160747</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.3028462500191683</v>
+        <v>-0.3029674865534479</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.3880430271203037</v>
+        <v>-0.3736040075113636</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.4802282139869086</v>
+        <v>-0.4445106089307096</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.5417301710244475</v>
+        <v>-0.5442288826949627</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.5631671045083007</v>
+        <v>-0.5797835745850116</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.7362276911269341</v>
+        <v>-0.7375153599202096</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.4601170610148747</v>
+        <v>-0.4499872699761547</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.5898375212123771</v>
+        <v>-0.576093801241695</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.0290463298634079</v>
+        <v>0.07539824510972377</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.1262062334229771</v>
+        <v>0.1358509140486471</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-0.003575677425354407</v>
+        <v>-0.09561808605976557</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.219219198823669</v>
+        <v>-0.1557774621208786</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.08182953899337868</v>
+        <v>-0.1112431819890909</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.1600429283466341</v>
+        <v>-0.1173551294726765</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-7.309415476190139</v>
+        <v>-8.95382336468643</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-2.793653136661256</v>
+        <v>-3.335318155249278</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-7.210618359968879</v>
+        <v>-9.317328320171772</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.6812283183843859</v>
+        <v>0.1416428371087491</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-7.004407013576608</v>
+        <v>-9.005486550468286</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-0.9393811767214183</v>
+        <v>-1.223053592705139</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-17.88416911838908</v>
+        <v>-18.25967666260673</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-14.36806273946674</v>
+        <v>-15.57775597268442</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-16.06764742249276</v>
+        <v>-17.70476215522844</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-12.48811419914903</v>
+        <v>-10.58302343225644</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-13.77612005615408</v>
+        <v>-14.78779961638527</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-8.581176190899736</v>
+        <v>-9.90809712512363</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2.499049039384278</v>
+        <v>0.2557292714335079</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>10.43653962209756</v>
+        <v>11.41816713915919</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.72365101993882</v>
+        <v>-1.879039606025711</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>13.56477784266153</v>
+        <v>14.83117076167498</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.1158853242148835</v>
+        <v>-2.799211651422493</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>9.030721838746102</v>
+        <v>7.511829819182164</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.2442063453960184</v>
+        <v>-0.3095782314095032</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.09333548284818037</v>
+        <v>-0.1153185464616588</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.3250886263801663</v>
+        <v>-0.4124752212071652</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.0307129801105999</v>
+        <v>0.006270484259136279</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.2707382711136613</v>
+        <v>-0.3507659629347374</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.03630948847051775</v>
+        <v>-0.04763824461474545</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.5168580596527215</v>
+        <v>-0.5369276515251594</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.423455492007176</v>
+        <v>-0.4621270378427287</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.6002762724895013</v>
+        <v>-0.6497278457885174</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.5264406340884543</v>
+        <v>-0.4305453814153208</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.4789219656706536</v>
+        <v>-0.5081608379884968</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.3130909848014099</v>
+        <v>-0.3582429480246013</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.09981523173905685</v>
+        <v>0.01506682732541272</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.4215521572406526</v>
+        <v>0.4568596506413228</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.05061791014470293</v>
+        <v>-0.09523190191539463</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.7265782237018998</v>
+        <v>0.7874707558135018</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.0007518005418190621</v>
+        <v>-0.1191997389873464</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.4330254191496684</v>
+        <v>0.3238646495413308</v>
       </c>
     </row>
     <row r="34">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>-7.914836513943293</v>
+        <v>-4.488678204717922</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>-13.36651863440237</v>
+        <v>-10.11815169966241</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-11.68053501222098</v>
+        <v>-14.8770277019706</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-20.17464960184433</v>
+        <v>-21.69505153871948</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-9.758921196028131</v>
+        <v>-9.136698829801674</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-16.42426171572417</v>
+        <v>-15.20415259467527</v>
       </c>
     </row>
     <row r="35">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>-22.94674767756598</v>
+        <v>-16.93312871436548</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>-27.79255993816516</v>
+        <v>-24.17625103895242</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-25.82128282386926</v>
+        <v>-28.4758021440044</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-34.85297783987313</v>
+        <v>-35.25700787261081</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-20.09969783117434</v>
+        <v>-18.50043830440555</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-27.03272652638032</v>
+        <v>-25.28365605158423</v>
       </c>
     </row>
     <row r="36">
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>7.513607826223442</v>
+        <v>8.522371884223288</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2.59565946845037</v>
+        <v>6.183190018721471</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>4.449482044366004</v>
+        <v>-0.3913424313311331</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-3.191883938240848</v>
+        <v>-6.243417488032105</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.02138454453870491</v>
+        <v>1.307987024132478</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-3.994332240213552</v>
+        <v>-3.636930650294591</v>
       </c>
     </row>
     <row r="37">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>-0.2543184013965608</v>
+        <v>-0.1610380920703008</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>-0.4294910760759279</v>
+        <v>-0.3630039336031887</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-0.4113958154716889</v>
+        <v>-0.4973456848868098</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.7105638925034298</v>
+        <v>-0.725275268846199</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.3258952223226348</v>
+        <v>-0.3180763970573534</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.5484815704331708</v>
+        <v>-0.5293029974732676</v>
       </c>
     </row>
     <row r="38">
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>-0.5946755401753188</v>
+        <v>-0.507378045145721</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>-0.7652055376349897</v>
+        <v>-0.7297136746882587</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-0.7189108159639798</v>
+        <v>-0.7646154331621288</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.9423188570103185</v>
+        <v>-0.9439233903698274</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.5653831725828506</v>
+        <v>-0.5585976311484405</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.7789355350358157</v>
+        <v>-0.7798471943099349</v>
       </c>
     </row>
     <row r="39">
@@ -1531,22 +1531,22 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.3246887781692643</v>
+        <v>0.3993168561502314</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.1190986748231477</v>
+        <v>0.3416910952960389</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.2752042512998105</v>
+        <v>0.06140259292294294</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.06098201189033221</v>
+        <v>-0.1023042242464754</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.05088508199409907</v>
+        <v>0.05892129611812055</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.1589050440045148</v>
+        <v>-0.1197343199763168</v>
       </c>
     </row>
     <row r="40">
@@ -1561,22 +1561,22 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>-7.302926601363438</v>
+        <v>-6.229720535779354</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>-8.946729553102889</v>
+        <v>-7.383873874212096</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-8.678854308779933</v>
+        <v>-8.933113077769253</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-10.63885230469394</v>
+        <v>-9.686953614072292</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-7.882998305968488</v>
+        <v>-7.461128631789618</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>-9.4164652487129</v>
+        <v>-8.22050148226924</v>
       </c>
     </row>
     <row r="41">
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>-12.09482512117554</v>
+        <v>-10.33953712045326</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>-14.15612182294687</v>
+        <v>-11.93559501790714</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-12.72316411633649</v>
+        <v>-12.57526230087456</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-15.14211940551653</v>
+        <v>-14.00155537216665</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-10.94320218183192</v>
+        <v>-10.08140921459511</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-12.97212965436586</v>
+        <v>-11.35119186002368</v>
       </c>
     </row>
     <row r="42">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-2.827346327087186</v>
+        <v>-2.09903026681148</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>-3.723737007647522</v>
+        <v>-2.077965313111652</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-4.678830213363695</v>
+        <v>-5.2416664323949</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-5.776828196389113</v>
+        <v>-5.183529578055582</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-4.681491578793177</v>
+        <v>-4.822079679781909</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-5.864578566787083</v>
+        <v>-4.890442705051657</v>
       </c>
     </row>
     <row r="43">
@@ -1639,22 +1639,22 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>-0.2568958049105676</v>
+        <v>-0.238873710806046</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>-0.31472003147785</v>
+        <v>-0.2831288084797212</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-0.3886509761537916</v>
+        <v>-0.4143286091517271</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-0.4764223693895128</v>
+        <v>-0.4492926466837166</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.3100280708074274</v>
+        <v>-0.3125514577162688</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.3703373312503807</v>
+        <v>-0.3443620728497913</v>
       </c>
     </row>
     <row r="44">
@@ -1665,22 +1665,22 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>-0.389671490378226</v>
+        <v>-0.3615276042232201</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>-0.4515663272334705</v>
+        <v>-0.4314947182311234</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-0.5125714940648337</v>
+        <v>-0.5302255307215304</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.6345249342798293</v>
+        <v>-0.5928396805408885</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.3983086449368398</v>
+        <v>-0.3992111495457448</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.4895475662412862</v>
+        <v>-0.4578290886995209</v>
       </c>
     </row>
     <row r="45">
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>-0.1000362304231254</v>
+        <v>-0.08620734634587116</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>-0.1246310959624665</v>
+        <v>-0.08971044304818936</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-0.2266181617930882</v>
+        <v>-0.270376816023767</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-0.2824425269737028</v>
+        <v>-0.2611281047328957</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.1991503061466587</v>
+        <v>-0.2139319506383455</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.2395529302539793</v>
+        <v>-0.2172701121283709</v>
       </c>
     </row>
     <row r="46">
